--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_recharge.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_recharge.xlsx
@@ -200,22 +200,16 @@
     <t>30030307#1</t>
   </si>
   <si>
-    <t>充值档位6元</t>
-  </si>
-  <si>
-    <t>10240001#60</t>
-  </si>
-  <si>
-    <t>充值档位30元</t>
-  </si>
-  <si>
-    <t>10240001#300</t>
-  </si>
-  <si>
-    <t>充值档位68元</t>
-  </si>
-  <si>
-    <t>10240001#680</t>
+    <t>充值档位58元</t>
+  </si>
+  <si>
+    <t>10240001#580</t>
+  </si>
+  <si>
+    <t>充值档位98元</t>
+  </si>
+  <si>
+    <t>10240001#980</t>
   </si>
   <si>
     <t>充值档位128元</t>
@@ -224,6 +218,12 @@
     <t>10240001#1280</t>
   </si>
   <si>
+    <t>充值档位258元</t>
+  </si>
+  <si>
+    <t>10240001#2580</t>
+  </si>
+  <si>
     <t>充值档位328元</t>
   </si>
   <si>
@@ -248,10 +248,10 @@
     <t>10240001#29980</t>
   </si>
   <si>
-    <t>充值档位5000元</t>
-  </si>
-  <si>
-    <t>10240001#50000</t>
+    <t>充值档位5888元</t>
+  </si>
+  <si>
+    <t>10240001#58880</t>
   </si>
   <si>
     <t>首充6元</t>
@@ -884,7 +884,7 @@
     <t>合成保护符咒</t>
   </si>
   <si>
-    <t>50040038#1</t>
+    <t>1254003899#1</t>
   </si>
   <si>
     <t>光明法师角色</t>
@@ -893,7 +893,7 @@
     <t>60080004#1</t>
   </si>
   <si>
-    <t>星澜战旗</t>
+    <t>雷霆战旗</t>
   </si>
   <si>
     <t>2000000199#1</t>
@@ -2160,7 +2160,7 @@
         <v>36</v>
       </c>
       <c r="H7" s="6">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:9">
@@ -2182,7 +2182,7 @@
         <v>38</v>
       </c>
       <c r="H8" s="6">
-        <v>30</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:9">
@@ -2204,7 +2204,7 @@
         <v>40</v>
       </c>
       <c r="H9" s="6">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:9">
@@ -2226,7 +2226,7 @@
         <v>42</v>
       </c>
       <c r="H10" s="6">
-        <v>128</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:9">
@@ -2336,7 +2336,7 @@
         <v>52</v>
       </c>
       <c r="H15" s="6">
-        <v>5000</v>
+        <v>5888</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:9">
@@ -7279,7 +7279,7 @@
         <v>180</v>
       </c>
       <c r="H222" s="4">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -7348,7 +7348,7 @@
         <v>180</v>
       </c>
       <c r="H225" s="4">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -7408,7 +7408,7 @@
         <v>191</v>
       </c>
       <c r="H228" s="4">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -7428,7 +7428,7 @@
         <v>193</v>
       </c>
       <c r="H229" s="4">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="230" spans="1:8">

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_recharge.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_recharge.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_recharge" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="185">
   <si>
     <t>唯一id</t>
   </si>
@@ -203,55 +203,55 @@
     <t>充值档位58元</t>
   </si>
   <si>
-    <t>10240001#580</t>
+    <t>10040001#58</t>
   </si>
   <si>
     <t>充值档位98元</t>
   </si>
   <si>
-    <t>10240001#980</t>
+    <t>10040001#98</t>
   </si>
   <si>
     <t>充值档位128元</t>
   </si>
   <si>
-    <t>10240001#1280</t>
+    <t>10040001#128</t>
   </si>
   <si>
     <t>充值档位258元</t>
   </si>
   <si>
-    <t>10240001#2580</t>
+    <t>10040001#258</t>
   </si>
   <si>
     <t>充值档位328元</t>
   </si>
   <si>
-    <t>10240001#3280</t>
+    <t>10040001#328</t>
   </si>
   <si>
     <t>充值档位648元</t>
   </si>
   <si>
-    <t>10240001#6480</t>
+    <t>10040001#648</t>
   </si>
   <si>
     <t>充值档位998元</t>
   </si>
   <si>
-    <t>10240001#9980</t>
+    <t>10040001#998</t>
   </si>
   <si>
     <t>充值档位2998元</t>
   </si>
   <si>
-    <t>10240001#29980</t>
+    <t>10040001#2998</t>
   </si>
   <si>
     <t>充值档位5888元</t>
   </si>
   <si>
-    <t>10240001#58880</t>
+    <t>10040001#5888</t>
   </si>
   <si>
     <t>首充6元</t>
@@ -858,45 +858,6 @@
   </si>
   <si>
     <t>30031064#1|30032003#1</t>
-  </si>
-  <si>
-    <t>强化天使</t>
-  </si>
-  <si>
-    <t>直充商品</t>
-  </si>
-  <si>
-    <t>2140000899#1</t>
-  </si>
-  <si>
-    <t>强化恶魔</t>
-  </si>
-  <si>
-    <t>2140000799#1</t>
-  </si>
-  <si>
-    <t>幸运宝石</t>
-  </si>
-  <si>
-    <t>1254006799#1</t>
-  </si>
-  <si>
-    <t>合成保护符咒</t>
-  </si>
-  <si>
-    <t>1254003899#1</t>
-  </si>
-  <si>
-    <t>光明法师角色</t>
-  </si>
-  <si>
-    <t>60080004#1</t>
-  </si>
-  <si>
-    <t>雷霆战旗</t>
-  </si>
-  <si>
-    <t>2000000199#1</t>
   </si>
 </sst>
 </file>
@@ -1961,7 +1922,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J231"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.2666666666667" style="4" customWidth="1"/>
@@ -7351,129 +7312,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
-      <c r="A226" s="4">
-        <v>4002</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D226" s="4">
-        <v>22</v>
-      </c>
-      <c r="G226" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="H226" s="4">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8">
-      <c r="A227" s="4">
-        <v>4003</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D227" s="4">
-        <v>22</v>
-      </c>
-      <c r="G227" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="H227" s="4">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8">
-      <c r="A228" s="4">
-        <v>4004</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D228" s="4">
-        <v>22</v>
-      </c>
-      <c r="G228" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="H228" s="4">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8">
-      <c r="A229" s="4">
-        <v>4005</v>
-      </c>
-      <c r="B229" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D229" s="4">
-        <v>22</v>
-      </c>
-      <c r="G229" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H229" s="4">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8">
-      <c r="A230" s="4">
-        <v>4006</v>
-      </c>
-      <c r="B230" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D230" s="4">
-        <v>22</v>
-      </c>
-      <c r="G230" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H230" s="4">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8">
-      <c r="A231" s="4">
-        <v>4007</v>
-      </c>
-      <c r="B231" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D231" s="4">
-        <v>22</v>
-      </c>
-      <c r="G231" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H231" s="4">
-        <v>288</v>
-      </c>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B15">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7481,22 +7322,22 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C15">
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C72">
-    <cfRule type="duplicateValues" dxfId="1" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="1" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C73">
-    <cfRule type="duplicateValues" dxfId="1" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B224">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7504,14 +7345,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C224">
-    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A225:C225">
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7519,31 +7363,14 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A231">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B231:C231">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B231">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A242:C242">
-    <cfRule type="duplicateValues" dxfId="1" priority="220"/>
+  <conditionalFormatting sqref="A234:C234">
+    <cfRule type="duplicateValues" dxfId="1" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:B101">
-    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
-    <cfRule type="colorScale" priority="114">
+    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
+    <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7553,8 +7380,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B102:B111">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-    <cfRule type="colorScale" priority="67">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+    <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7564,8 +7391,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:B121">
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-    <cfRule type="colorScale" priority="63">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+    <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7575,7 +7402,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122:B131">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7583,11 +7410,11 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132:B141">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-    <cfRule type="colorScale" priority="54">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+    <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7597,8 +7424,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142:B151">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-    <cfRule type="colorScale" priority="50">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+    <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7608,8 +7435,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152:B161">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-    <cfRule type="colorScale" priority="47">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7619,7 +7446,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B162:B171">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7627,10 +7454,10 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172:B181">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7638,10 +7465,10 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182:B191">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7649,10 +7476,10 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192:B201">
-    <cfRule type="colorScale" priority="35">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7660,10 +7487,10 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202:B211">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7671,10 +7498,10 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B212:B221">
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7682,11 +7509,11 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222:B223">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7696,28 +7523,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E108:E111">
-    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E118:E121">
-    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E128:E131">
-    <cfRule type="duplicateValues" dxfId="1" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E138:E141">
-    <cfRule type="duplicateValues" dxfId="1" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E163">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F222:F225">
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:C6 B7:C14 A16:C37 A38 A39:C71 A72:B72 A73:A81 A82:C91 A92:A221 B226:C230 A232:C232 A236:C241">
-    <cfRule type="duplicateValues" dxfId="1" priority="221"/>
+  <conditionalFormatting sqref="A1:C6 B7:C14 A16:C37 A38 A39:C71 A72:B72 A73:A81 A82:C91 A92:A221 A228:C233">
+    <cfRule type="duplicateValues" dxfId="1" priority="231"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B14 B16:B91 B226:B230 B232:B1048576">
-    <cfRule type="colorScale" priority="203">
+  <conditionalFormatting sqref="B1:B14 B16:B91 B226:B1048576">
+    <cfRule type="colorScale" priority="213">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7725,58 +7552,55 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74:C81">
-    <cfRule type="duplicateValues" dxfId="1" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:C101">
-    <cfRule type="duplicateValues" dxfId="1" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B102:C111">
-    <cfRule type="duplicateValues" dxfId="1" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112:C121">
-    <cfRule type="duplicateValues" dxfId="1" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122:C131">
-    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132:C141">
+    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B142:C151">
+    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B152:C161">
+    <cfRule type="duplicateValues" dxfId="1" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B162:C171">
     <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142:C151">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B152:C161">
-    <cfRule type="duplicateValues" dxfId="1" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B162:C171">
-    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B172:C181">
-    <cfRule type="duplicateValues" dxfId="1" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182:C191">
-    <cfRule type="duplicateValues" dxfId="1" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192:C201">
-    <cfRule type="duplicateValues" dxfId="1" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202:C211">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B212:C221">
-    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A222:C223 A224">
-    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A225:C225 A226:A230">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A233:C235">
-    <cfRule type="duplicateValues" dxfId="1" priority="219"/>
+  <conditionalFormatting sqref="A226:C227">
+    <cfRule type="duplicateValues" dxfId="1" priority="229"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
